--- a/tooltask/reports/pr_report.xlsx
+++ b/tooltask/reports/pr_report.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,14 +435,149 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Create list_prs.yml</t>
+          <t>Update requirements.txt</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Update README.md</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Mounashree-2310</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Update list_prs.yml</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>Mounashree-2310</t>
         </is>
